--- a/backend/sample_data/07_Invalid_Bounds_Validation_Test.xlsx
+++ b/backend/sample_data/07_Invalid_Bounds_Validation_Test.xlsx
@@ -453,7 +453,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>SU2026-0020</t>
+          <t>SU2026-0010</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -471,7 +471,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>SU2026-0020</t>
+          <t>SU2026-0010</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -489,7 +489,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>SU2026-0020</t>
+          <t>SU2026-0010</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
